--- a/REFERENCE_PROPERTIES/TC_Measurement_Data.xlsx
+++ b/REFERENCE_PROPERTIES/TC_Measurement_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutk-my.sharepoint.com/personal/jnumbers_vols_utk_edu/Documents/Documents/2026-Structural-Coherence-Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qcn\Documents\Molten-Salt-TP-Suite-Codes-Development\REFERENCE_PROPERTIES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{C4E62733-C08C-4ABA-84A1-FEF52F230632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{547EE345-4960-4B4C-B65D-953D678455F7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59882EB1-40AC-4F29-B087-D82952934AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30465" yWindow="1725" windowWidth="19185" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -486,9 +486,6 @@
     <t>0.675LiF-0.20BeF2-0.12ThF4-0.005UF4 (Rosenthal, 1969)</t>
   </si>
   <si>
-    <t>0.1511NaCl-0.3891KCl-0.4598MgCl2 (Wang, 2021)</t>
-  </si>
-  <si>
     <t>0.66LiF-0.34BeF2 (Redkin, 2022)</t>
   </si>
   <si>
@@ -571,6 +568,9 @@
   </si>
   <si>
     <t>0.6LiF-0.4NaF (Ruth, 2023)</t>
+  </si>
+  <si>
+    <t>0.21NaCl-0.41KCl-0.38MgCl2 (Wang, 2021)</t>
   </si>
 </sst>
 </file>
@@ -852,10 +852,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2645,7 +2641,7 @@
         <v>13</v>
       </c>
       <c r="B69" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D69" s="34">
         <v>761.2</v>
@@ -2671,7 +2667,7 @@
         <v>13</v>
       </c>
       <c r="B70" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D70" s="34">
         <v>811.3</v>
@@ -2697,7 +2693,7 @@
         <v>13</v>
       </c>
       <c r="B71" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D71" s="34">
         <v>860.5</v>
@@ -2723,7 +2719,7 @@
         <v>13</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D72" s="34">
         <v>908.5</v>
@@ -2749,7 +2745,7 @@
         <v>13</v>
       </c>
       <c r="B73" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D73" s="34">
         <v>958.5</v>
@@ -2775,7 +2771,7 @@
         <v>13</v>
       </c>
       <c r="B74" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D74" s="34">
         <v>1008.2</v>
@@ -2801,7 +2797,7 @@
         <v>14</v>
       </c>
       <c r="B75" s="30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D75" s="34">
         <v>933.1</v>
@@ -2835,7 +2831,7 @@
         <v>14</v>
       </c>
       <c r="B76" s="30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D76" s="34">
         <v>950.7</v>
@@ -2861,7 +2857,7 @@
         <v>14</v>
       </c>
       <c r="B77" s="30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D77" s="34">
         <v>966.7</v>
@@ -2887,7 +2883,7 @@
         <v>14</v>
       </c>
       <c r="B78" s="30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D78" s="34">
         <v>986.7</v>
@@ -2913,7 +2909,7 @@
         <v>14</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D79" s="34">
         <v>1006.9</v>
@@ -11579,7 +11575,7 @@
         <v>208</v>
       </c>
       <c r="B643" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D643" s="1">
         <v>523.48130841121497</v>
@@ -11593,7 +11589,7 @@
         <v>208</v>
       </c>
       <c r="B644" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D644" s="1">
         <v>573.24766355140196</v>
@@ -11607,7 +11603,7 @@
         <v>208</v>
       </c>
       <c r="B645" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D645" s="1">
         <v>623.36448598130801</v>
@@ -11621,7 +11617,7 @@
         <v>208</v>
       </c>
       <c r="B646" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D646" s="1">
         <v>648.24766355140196</v>
@@ -11635,7 +11631,7 @@
         <v>208</v>
       </c>
       <c r="B647" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D647" s="1">
         <v>673.130841121495</v>
@@ -11649,7 +11645,7 @@
         <v>208</v>
       </c>
       <c r="B648" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D648" s="1">
         <v>698.36448598130801</v>
@@ -11663,7 +11659,7 @@
         <v>209</v>
       </c>
       <c r="B649" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D649" s="1">
         <v>522.63401720714705</v>
@@ -11677,7 +11673,7 @@
         <v>209</v>
       </c>
       <c r="B650" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D650" s="1">
         <v>572.66710787557895</v>
@@ -11691,7 +11687,7 @@
         <v>209</v>
       </c>
       <c r="B651" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D651" s="1">
         <v>622.70019854401005</v>
@@ -11705,7 +11701,7 @@
         <v>209</v>
       </c>
       <c r="B652" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D652" s="1">
         <v>672.73328921244195</v>
@@ -11719,7 +11715,7 @@
         <v>209</v>
       </c>
       <c r="B653" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D653" s="1">
         <v>773.19655857048303</v>
@@ -11733,7 +11729,7 @@
         <v>209</v>
       </c>
       <c r="B654" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D654" s="1">
         <v>872.86565188616805</v>
@@ -11747,7 +11743,7 @@
         <v>209</v>
       </c>
       <c r="B655" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D655" s="1">
         <v>972.93183322303105</v>
@@ -11761,7 +11757,7 @@
         <v>209</v>
       </c>
       <c r="B656" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D656" s="1">
         <v>1072.6009265387099</v>
@@ -11890,7 +11886,7 @@
         <v>220</v>
       </c>
       <c r="B664" s="30" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="D664" s="1">
         <v>722.73280584297004</v>
@@ -11904,7 +11900,7 @@
         <v>220</v>
       </c>
       <c r="B665" s="30" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="D665" s="1">
         <v>772.94583079732195</v>
@@ -11918,7 +11914,7 @@
         <v>220</v>
       </c>
       <c r="B666" s="30" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="D666" s="1">
         <v>822.85453438831405</v>
@@ -11932,7 +11928,7 @@
         <v>220</v>
       </c>
       <c r="B667" s="30" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="D667" s="1">
         <v>873.06755934266505</v>
@@ -11946,7 +11942,7 @@
         <v>220</v>
       </c>
       <c r="B668" s="30" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="D668" s="1">
         <v>922.97626293365704</v>
@@ -11960,7 +11956,7 @@
         <v>220</v>
       </c>
       <c r="B669" s="30" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="D669" s="1">
         <v>973.18928788800895</v>
@@ -11974,7 +11970,7 @@
         <v>230</v>
       </c>
       <c r="B670" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D670" s="1">
         <v>742</v>
@@ -11988,7 +11984,7 @@
         <v>230</v>
       </c>
       <c r="B671" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D671" s="1">
         <v>748</v>
@@ -12002,7 +11998,7 @@
         <v>240</v>
       </c>
       <c r="B672" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D672" s="1">
         <v>750.14153147936395</v>
@@ -12016,7 +12012,7 @@
         <v>240</v>
       </c>
       <c r="B673" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D673" s="1">
         <v>752.13939601477898</v>
@@ -12030,7 +12026,7 @@
         <v>240</v>
       </c>
       <c r="B674" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D674" s="1">
         <v>766.52402066976799</v>
@@ -12044,7 +12040,7 @@
         <v>240</v>
       </c>
       <c r="B675" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D675" s="1">
         <v>763.19424644407604</v>
@@ -12058,7 +12054,7 @@
         <v>240</v>
       </c>
       <c r="B676" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D676" s="1">
         <v>748.14366694394801</v>
@@ -12072,7 +12068,7 @@
         <v>240</v>
       </c>
       <c r="B677" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D677" s="1">
         <v>746.27899337756105</v>
@@ -12086,7 +12082,7 @@
         <v>240</v>
       </c>
       <c r="B678" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D678" s="1">
         <v>757.20065283783094</v>
@@ -12100,7 +12096,7 @@
         <v>240</v>
       </c>
       <c r="B679" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D679" s="1">
         <v>759.33170834227303</v>
@@ -12114,7 +12110,7 @@
         <v>240</v>
       </c>
       <c r="B680" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D680" s="1">
         <v>761.72914578477196</v>
@@ -12128,7 +12124,7 @@
         <v>240</v>
       </c>
       <c r="B681" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D681" s="1">
         <v>771.31889555476505</v>
@@ -12142,7 +12138,7 @@
         <v>240</v>
       </c>
       <c r="B682" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D682" s="1">
         <v>766.39082970074105</v>
@@ -12156,7 +12152,7 @@
         <v>240</v>
       </c>
       <c r="B683" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D683" s="1">
         <v>774.91505171851202</v>
@@ -12170,7 +12166,7 @@
         <v>240</v>
       </c>
       <c r="B684" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D684" s="1">
         <v>781.44140920086795</v>
@@ -12184,7 +12180,7 @@
         <v>240</v>
       </c>
       <c r="B685" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D685" s="1">
         <v>784.10522858142201</v>
@@ -12198,7 +12194,7 @@
         <v>240</v>
       </c>
       <c r="B686" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D686" s="1">
         <v>796.89156160807897</v>
@@ -12212,7 +12208,7 @@
         <v>240</v>
       </c>
       <c r="B687" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D687" s="1">
         <v>797.95708936030098</v>
@@ -12226,7 +12222,7 @@
         <v>240</v>
       </c>
       <c r="B688" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D688" s="1">
         <v>795.69284288683002</v>
@@ -12240,7 +12236,7 @@
         <v>240</v>
       </c>
       <c r="B689" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D689" s="1">
         <v>793.56178738238702</v>
@@ -12254,7 +12250,7 @@
         <v>240</v>
       </c>
       <c r="B690" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D690" s="1">
         <v>789.03329443544601</v>
@@ -12268,7 +12264,7 @@
         <v>240</v>
       </c>
       <c r="B691" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D691" s="1">
         <v>804.08387393557405</v>
@@ -12282,7 +12278,7 @@
         <v>240</v>
       </c>
       <c r="B692" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D692" s="1">
         <v>816.33744308612097</v>
@@ -12296,7 +12292,7 @@
         <v>240</v>
       </c>
       <c r="B693" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D693" s="1">
         <v>823.39656444458797</v>
@@ -12310,7 +12306,7 @@
         <v>240</v>
       </c>
       <c r="B694" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D694" s="1">
         <v>824.86166510389205</v>
@@ -12324,7 +12320,7 @@
         <v>240</v>
       </c>
       <c r="B695" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D695" s="1">
         <v>829.12377611277805</v>
@@ -12338,7 +12334,7 @@
         <v>240</v>
       </c>
       <c r="B696" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D696" s="1">
         <v>835.51694262610704</v>
@@ -12352,7 +12348,7 @@
         <v>240</v>
       </c>
       <c r="B697" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D697" s="1">
         <v>826.32676576319705</v>
@@ -12366,7 +12362,7 @@
         <v>240</v>
       </c>
       <c r="B698" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D698" s="1">
         <v>822.99699153750498</v>
@@ -12380,7 +12376,7 @@
         <v>240</v>
       </c>
       <c r="B699" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D699" s="1">
         <v>820.99912700208995</v>
@@ -12394,7 +12390,7 @@
         <v>240</v>
       </c>
       <c r="B700" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D700" s="1">
         <v>818.335307621536</v>
@@ -12408,7 +12404,7 @@
         <v>240</v>
       </c>
       <c r="B701" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D701" s="1">
         <v>855.76196991831398</v>
@@ -12422,7 +12418,7 @@
         <v>240</v>
       </c>
       <c r="B702" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D702" s="1">
         <v>852.83176859970501</v>
@@ -12436,7 +12432,7 @@
         <v>240</v>
       </c>
       <c r="B703" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D703" s="1">
         <v>866.81682034761104</v>
@@ -12450,7 +12446,7 @@
         <v>240</v>
       </c>
       <c r="B704" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D704" s="1">
         <v>878.271243683992</v>
@@ -12464,7 +12460,7 @@
         <v>240</v>
       </c>
       <c r="B705" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D705" s="1">
         <v>873.60955976802302</v>
@@ -12478,7 +12474,7 @@
         <v>240</v>
       </c>
       <c r="B706" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D706" s="1">
         <v>878.271243683992</v>
@@ -12492,7 +12488,7 @@
         <v>240</v>
       </c>
       <c r="B707" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D707" s="1">
         <v>875.07466042732801</v>
@@ -12506,7 +12502,7 @@
         <v>240</v>
       </c>
       <c r="B708" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D708" s="1">
         <v>870.67935844941405</v>
@@ -12520,7 +12516,7 @@
         <v>240</v>
       </c>
       <c r="B709" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D709" s="1">
         <v>874.94146945830005</v>
@@ -12534,7 +12530,7 @@
         <v>250</v>
       </c>
       <c r="B710" s="33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C710" s="31"/>
       <c r="D710" s="1">
@@ -12549,7 +12545,7 @@
         <v>250</v>
       </c>
       <c r="B711" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C711" s="3"/>
       <c r="D711" s="1">
@@ -12564,7 +12560,7 @@
         <v>250</v>
       </c>
       <c r="B712" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C712" s="3"/>
       <c r="D712" s="1">
@@ -12579,7 +12575,7 @@
         <v>250</v>
       </c>
       <c r="B713" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C713" s="3"/>
       <c r="D713" s="1">
@@ -12594,7 +12590,7 @@
         <v>250</v>
       </c>
       <c r="B714" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C714" s="3"/>
       <c r="D714" s="1">
@@ -12609,7 +12605,7 @@
         <v>250</v>
       </c>
       <c r="B715" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C715" s="3"/>
       <c r="D715" s="1">
@@ -12624,7 +12620,7 @@
         <v>250</v>
       </c>
       <c r="B716" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C716" s="3"/>
       <c r="D716" s="1">
@@ -12639,7 +12635,7 @@
         <v>260</v>
       </c>
       <c r="B717" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D717" s="1">
         <v>733</v>
@@ -12654,7 +12650,7 @@
         <v>260</v>
       </c>
       <c r="B718" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D718" s="1">
         <v>755</v>
@@ -12669,7 +12665,7 @@
         <v>260</v>
       </c>
       <c r="B719" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D719" s="1">
         <v>777</v>
@@ -12684,7 +12680,7 @@
         <v>260</v>
       </c>
       <c r="B720" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D720" s="1">
         <v>799</v>
@@ -12699,7 +12695,7 @@
         <v>260</v>
       </c>
       <c r="B721" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D721" s="1">
         <v>821</v>
@@ -12714,7 +12710,7 @@
         <v>260</v>
       </c>
       <c r="B722" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D722" s="1">
         <v>843</v>
@@ -12729,7 +12725,7 @@
         <v>260</v>
       </c>
       <c r="B723" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D723" s="1">
         <v>865</v>
@@ -12744,7 +12740,7 @@
         <v>260</v>
       </c>
       <c r="B724" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D724" s="1">
         <v>887</v>
@@ -12759,7 +12755,7 @@
         <v>260</v>
       </c>
       <c r="B725" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D725" s="1">
         <v>909</v>
@@ -12774,7 +12770,7 @@
         <v>260</v>
       </c>
       <c r="B726" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D726" s="1">
         <v>931</v>
@@ -12789,7 +12785,7 @@
         <v>260</v>
       </c>
       <c r="B727" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D727" s="1">
         <v>953</v>
@@ -12804,7 +12800,7 @@
         <v>260</v>
       </c>
       <c r="B728" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D728" s="1">
         <v>975</v>
@@ -12819,7 +12815,7 @@
         <v>260</v>
       </c>
       <c r="B729" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D729" s="1">
         <v>997</v>
@@ -12834,7 +12830,7 @@
         <v>260</v>
       </c>
       <c r="B730" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D730" s="1">
         <v>1019</v>
@@ -12849,7 +12845,7 @@
         <v>260</v>
       </c>
       <c r="B731" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D731" s="1">
         <v>1041</v>
@@ -12864,7 +12860,7 @@
         <v>260</v>
       </c>
       <c r="B732" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D732" s="1">
         <v>1063</v>
@@ -12879,7 +12875,7 @@
         <v>260</v>
       </c>
       <c r="B733" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D733" s="1">
         <v>1085</v>
@@ -12894,7 +12890,7 @@
         <v>260</v>
       </c>
       <c r="B734" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D734" s="1">
         <v>1107</v>
@@ -12909,7 +12905,7 @@
         <v>260</v>
       </c>
       <c r="B735" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D735" s="1">
         <v>1129</v>
@@ -12924,7 +12920,7 @@
         <v>260</v>
       </c>
       <c r="B736" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D736" s="1">
         <v>1150</v>
@@ -12939,7 +12935,7 @@
         <v>270</v>
       </c>
       <c r="B737" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D737" s="1">
         <v>792.88235294117601</v>
@@ -12953,7 +12949,7 @@
         <v>270</v>
       </c>
       <c r="B738" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D738" s="1">
         <v>872.82352941176396</v>
@@ -12967,7 +12963,7 @@
         <v>270</v>
       </c>
       <c r="B739" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D739" s="1">
         <v>922.94117647058795</v>
@@ -12981,7 +12977,7 @@
         <v>270</v>
       </c>
       <c r="B740" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D740" s="1">
         <v>972.88235294117601</v>
@@ -12995,7 +12991,7 @@
         <v>280</v>
       </c>
       <c r="B741" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D741" s="1">
         <v>822.88235294117601</v>
@@ -13009,7 +13005,7 @@
         <v>280</v>
       </c>
       <c r="B742" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D742" s="1">
         <v>873</v>
@@ -13023,7 +13019,7 @@
         <v>280</v>
       </c>
       <c r="B743" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D743" s="1">
         <v>922.94117647058795</v>
@@ -13037,7 +13033,7 @@
         <v>280</v>
       </c>
       <c r="B744" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D744" s="1">
         <v>973.05882352941103</v>
@@ -13051,7 +13047,7 @@
         <v>290</v>
       </c>
       <c r="B745" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D745" s="1">
         <v>792.94975688816805</v>
@@ -13065,7 +13061,7 @@
         <v>290</v>
       </c>
       <c r="B746" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D746" s="1">
         <v>822.93354943273903</v>
@@ -13079,7 +13075,7 @@
         <v>290</v>
       </c>
       <c r="B747" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D747" s="1">
         <v>923.01458670988598</v>
@@ -13093,7 +13089,7 @@
         <v>290</v>
       </c>
       <c r="B748" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D748" s="1">
         <v>1022.69043760129</v>
@@ -13107,7 +13103,7 @@
         <v>290</v>
       </c>
       <c r="B749" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D749" s="1">
         <v>1122.7714748784399</v>
@@ -13121,7 +13117,7 @@
         <v>290</v>
       </c>
       <c r="B750" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D750" s="1">
         <v>1222.8525121555899</v>
@@ -13135,7 +13131,7 @@
         <v>300</v>
       </c>
       <c r="B751" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D751" s="1">
         <v>849.27066450567202</v>
@@ -13155,7 +13151,7 @@
         <v>300</v>
       </c>
       <c r="B752" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D752" s="1">
         <v>874.39222042139295</v>
@@ -13175,7 +13171,7 @@
         <v>300</v>
       </c>
       <c r="B753" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D753" s="1">
         <v>899.10858995137698</v>
@@ -13195,7 +13191,7 @@
         <v>310</v>
       </c>
       <c r="B754" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D754">
         <v>1070</v>
@@ -13209,7 +13205,7 @@
         <v>310</v>
       </c>
       <c r="B755" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D755">
         <v>1080</v>
@@ -13223,7 +13219,7 @@
         <v>310</v>
       </c>
       <c r="B756" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D756">
         <v>1090</v>
@@ -13237,7 +13233,7 @@
         <v>310</v>
       </c>
       <c r="B757" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D757">
         <v>1100</v>
@@ -13251,7 +13247,7 @@
         <v>310</v>
       </c>
       <c r="B758" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D758">
         <v>1110</v>
@@ -13265,7 +13261,7 @@
         <v>310</v>
       </c>
       <c r="B759" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D759">
         <v>1120</v>
@@ -13279,7 +13275,7 @@
         <v>310</v>
       </c>
       <c r="B760" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D760">
         <v>1130</v>
@@ -13293,7 +13289,7 @@
         <v>320</v>
       </c>
       <c r="B761" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D761" s="1">
         <v>1099.77997799779</v>
@@ -13307,7 +13303,7 @@
         <v>320</v>
       </c>
       <c r="B762" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D762" s="1">
         <v>1199.88998899889</v>
@@ -13321,7 +13317,7 @@
         <v>320</v>
       </c>
       <c r="B763" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D763" s="1">
         <v>1249.8349834983401</v>
@@ -13335,7 +13331,7 @@
         <v>320</v>
       </c>
       <c r="B764" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D764" s="1">
         <v>1300</v>
@@ -13349,7 +13345,7 @@
         <v>330</v>
       </c>
       <c r="B765" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D765" s="1">
         <v>600</v>
@@ -13358,7 +13354,7 @@
         <v>0.69</v>
       </c>
       <c r="I765" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="766" spans="1:9" x14ac:dyDescent="0.25">
@@ -13366,7 +13362,7 @@
         <v>330</v>
       </c>
       <c r="B766" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D766" s="1">
         <v>620</v>
@@ -13380,7 +13376,7 @@
         <v>330</v>
       </c>
       <c r="B767" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D767" s="1">
         <v>640</v>
@@ -13394,7 +13390,7 @@
         <v>330</v>
       </c>
       <c r="B768" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D768" s="1">
         <v>660</v>
@@ -13408,7 +13404,7 @@
         <v>330</v>
       </c>
       <c r="B769" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D769" s="1">
         <v>680</v>
@@ -13422,7 +13418,7 @@
         <v>330</v>
       </c>
       <c r="B770" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D770" s="1">
         <v>700</v>
@@ -13436,7 +13432,7 @@
         <v>330</v>
       </c>
       <c r="B771" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D771" s="1">
         <v>720</v>
@@ -13450,7 +13446,7 @@
         <v>330</v>
       </c>
       <c r="B772" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D772" s="1">
         <v>740</v>
@@ -13464,7 +13460,7 @@
         <v>330</v>
       </c>
       <c r="B773" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D773" s="1">
         <v>760</v>
@@ -13478,7 +13474,7 @@
         <v>330</v>
       </c>
       <c r="B774" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D774" s="1">
         <v>780</v>
@@ -13492,7 +13488,7 @@
         <v>330</v>
       </c>
       <c r="B775" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D775" s="1">
         <v>800</v>
@@ -13506,7 +13502,7 @@
         <v>330</v>
       </c>
       <c r="B776" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D776" s="1">
         <v>820</v>
@@ -13520,7 +13516,7 @@
         <v>330</v>
       </c>
       <c r="B777" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D777" s="1">
         <v>840</v>
@@ -13534,7 +13530,7 @@
         <v>330</v>
       </c>
       <c r="B778" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D778" s="1">
         <v>860</v>
@@ -13548,7 +13544,7 @@
         <v>330</v>
       </c>
       <c r="B779" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D779" s="1">
         <v>880</v>
@@ -13562,7 +13558,7 @@
         <v>330</v>
       </c>
       <c r="B780" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D780" s="1">
         <v>900</v>
@@ -13576,7 +13572,7 @@
         <v>330</v>
       </c>
       <c r="B781" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D781" s="1">
         <v>920</v>
@@ -13590,7 +13586,7 @@
         <v>330</v>
       </c>
       <c r="B782" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D782" s="1">
         <v>940</v>
@@ -13604,7 +13600,7 @@
         <v>330</v>
       </c>
       <c r="B783" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D783" s="1">
         <v>960</v>
@@ -13618,7 +13614,7 @@
         <v>341</v>
       </c>
       <c r="B784" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D784" s="1">
         <v>1000</v>
@@ -13632,7 +13628,7 @@
         <v>341</v>
       </c>
       <c r="B785" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D785" s="1">
         <v>1200</v>
@@ -13646,7 +13642,7 @@
         <v>342</v>
       </c>
       <c r="B786" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D786" s="1">
         <v>1000</v>
@@ -13660,7 +13656,7 @@
         <v>342</v>
       </c>
       <c r="B787" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D787" s="1">
         <v>1200</v>
@@ -13674,7 +13670,7 @@
         <v>343</v>
       </c>
       <c r="B788" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D788" s="1">
         <v>1000</v>
@@ -13688,7 +13684,7 @@
         <v>343</v>
       </c>
       <c r="B789" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D789" s="1">
         <v>1200</v>
@@ -13702,7 +13698,7 @@
         <v>344</v>
       </c>
       <c r="B790" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D790" s="1">
         <v>1000</v>
@@ -13716,7 +13712,7 @@
         <v>344</v>
       </c>
       <c r="B791" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D791" s="1">
         <v>1200</v>
@@ -13730,7 +13726,7 @@
         <v>345</v>
       </c>
       <c r="B792" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D792" s="1">
         <v>1000</v>
@@ -13744,7 +13740,7 @@
         <v>345</v>
       </c>
       <c r="B793" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D793" s="1">
         <v>1200</v>
@@ -13758,7 +13754,7 @@
         <v>346</v>
       </c>
       <c r="B794" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D794" s="1">
         <v>1000</v>
@@ -13772,7 +13768,7 @@
         <v>346</v>
       </c>
       <c r="B795" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D795" s="1">
         <v>1200</v>
@@ -13786,7 +13782,7 @@
         <v>347</v>
       </c>
       <c r="B796" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D796" s="1">
         <v>1000</v>
@@ -13800,7 +13796,7 @@
         <v>347</v>
       </c>
       <c r="B797" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D797" s="1">
         <v>1200</v>
@@ -13814,7 +13810,7 @@
         <v>348</v>
       </c>
       <c r="B798" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D798" s="1">
         <v>1000</v>
@@ -13828,7 +13824,7 @@
         <v>348</v>
       </c>
       <c r="B799" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D799" s="1">
         <v>1200</v>
@@ -13842,7 +13838,7 @@
         <v>349</v>
       </c>
       <c r="B800" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D800" s="1">
         <v>1000</v>
@@ -13856,7 +13852,7 @@
         <v>349</v>
       </c>
       <c r="B801" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D801" s="1">
         <v>1200</v>
@@ -13870,7 +13866,7 @@
         <v>350</v>
       </c>
       <c r="B802" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D802" s="1">
         <v>761.04532462229395</v>
@@ -13884,7 +13880,7 @@
         <v>350</v>
       </c>
       <c r="B803" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D803" s="1">
         <v>811.02490812576502</v>
@@ -13898,7 +13894,7 @@
         <v>350</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D804" s="1">
         <v>860.02449979583503</v>
@@ -13912,7 +13908,7 @@
         <v>350</v>
       </c>
       <c r="B805" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D805" s="1">
         <v>908.37076357697003</v>
@@ -13926,7 +13922,7 @@
         <v>350</v>
       </c>
       <c r="B806" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D806" s="1">
         <v>958.350347080441</v>
@@ -13940,7 +13936,7 @@
         <v>350</v>
       </c>
       <c r="B807" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D807" s="1">
         <v>1008.32993058391</v>
@@ -13954,7 +13950,7 @@
         <v>360</v>
       </c>
       <c r="B808" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D808">
         <v>949.26108374384205</v>
@@ -13968,7 +13964,7 @@
         <v>360</v>
       </c>
       <c r="B809" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D809">
         <v>948.97959183673402</v>
@@ -13982,7 +13978,7 @@
         <v>360</v>
       </c>
       <c r="B810" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D810">
         <v>949.54257565094997</v>
@@ -13996,7 +13992,7 @@
         <v>360</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D811">
         <v>948.69809992962701</v>
@@ -14010,7 +14006,7 @@
         <v>360</v>
       </c>
       <c r="B812" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D812">
         <v>948.97959183673402</v>
@@ -14024,7 +14020,7 @@
         <v>360</v>
       </c>
       <c r="B813" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D813">
         <v>974.31386347642501</v>
@@ -14038,7 +14034,7 @@
         <v>360</v>
       </c>
       <c r="B814" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D814">
         <v>974.31386347642501</v>
@@ -14052,7 +14048,7 @@
         <v>360</v>
       </c>
       <c r="B815" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D815">
         <v>974.31386347642501</v>
@@ -14066,7 +14062,7 @@
         <v>360</v>
       </c>
       <c r="B816" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D816">
         <v>1003.30752990851</v>
@@ -14080,7 +14076,7 @@
         <v>360</v>
       </c>
       <c r="B817" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D817">
         <v>1004.99648135116</v>
@@ -14094,7 +14090,7 @@
         <v>360</v>
       </c>
       <c r="B818" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D818">
         <v>1004.15200562983</v>
@@ -14108,7 +14104,7 @@
         <v>360</v>
       </c>
       <c r="B819" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D819">
         <v>1003.30752990851</v>
@@ -14122,7 +14118,7 @@
         <v>360</v>
       </c>
       <c r="B820" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D820">
         <v>1044.4053483462301</v>
@@ -14136,7 +14132,7 @@
         <v>360</v>
       </c>
       <c r="B821" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D821">
         <v>1044.4053483462301</v>
@@ -14150,7 +14146,7 @@
         <v>360</v>
       </c>
       <c r="B822" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D822">
         <v>1043.56087262491</v>
@@ -14164,7 +14160,7 @@
         <v>360</v>
       </c>
       <c r="B823" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D823">
         <v>1082.68824771287</v>
@@ -14178,7 +14174,7 @@
         <v>360</v>
       </c>
       <c r="B824" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D824">
         <v>1084.09570724841</v>
@@ -14192,7 +14188,7 @@
         <v>360</v>
       </c>
       <c r="B825" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D825">
         <v>1113.65235749472</v>
@@ -14206,7 +14202,7 @@
         <v>360</v>
       </c>
       <c r="B826" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D826">
         <v>1143.77199155524</v>
@@ -14220,7 +14216,7 @@
         <v>360</v>
       </c>
       <c r="B827" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D827">
         <v>1143.77199155524</v>
@@ -14234,7 +14230,7 @@
         <v>360</v>
       </c>
       <c r="B828" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D828">
         <v>1143.49049964813</v>
@@ -14248,7 +14244,7 @@
         <v>360</v>
       </c>
       <c r="B829" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D829">
         <v>953.76495425756502</v>
@@ -14262,7 +14258,7 @@
         <v>370</v>
       </c>
       <c r="B830" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D830">
         <v>954.04644616467203</v>
@@ -14276,7 +14272,7 @@
         <v>370</v>
       </c>
       <c r="B831" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D831">
         <v>952.92047853624194</v>
@@ -14290,7 +14286,7 @@
         <v>370</v>
       </c>
       <c r="B832" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D832">
         <v>988.66995073891599</v>
@@ -14304,7 +14300,7 @@
         <v>370</v>
       </c>
       <c r="B833" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D833">
         <v>988.66995073891599</v>
@@ -14318,7 +14314,7 @@
         <v>370</v>
       </c>
       <c r="B834" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D834">
         <v>988.66995073891599</v>
@@ -14332,7 +14328,7 @@
         <v>370</v>
       </c>
       <c r="B835" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D835">
         <v>1033.4271639690301</v>
@@ -14346,7 +14342,7 @@
         <v>370</v>
       </c>
       <c r="B836" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D836">
         <v>1033.70865587614</v>
@@ -14360,7 +14356,7 @@
         <v>370</v>
       </c>
       <c r="B837" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D837">
         <v>1073.9619985925401</v>
@@ -14374,7 +14370,7 @@
         <v>370</v>
       </c>
       <c r="B838" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D838">
         <v>1074.2434904996401</v>
@@ -14388,7 +14384,7 @@
         <v>370</v>
       </c>
       <c r="B839" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D839">
         <v>1073.9619985925401</v>
@@ -14402,7 +14398,7 @@
         <v>380</v>
       </c>
       <c r="B840" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D840">
         <v>933.49753694581204</v>
@@ -14416,7 +14412,7 @@
         <v>381</v>
       </c>
       <c r="B841" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D841">
         <v>950.66854327937995</v>
@@ -14430,7 +14426,7 @@
         <v>382</v>
       </c>
       <c r="B842" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D842">
         <v>971.49894440534797</v>
@@ -14444,7 +14440,7 @@
         <v>383</v>
       </c>
       <c r="B843" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D843">
         <v>988.951442646023</v>
@@ -14458,7 +14454,7 @@
         <v>384</v>
       </c>
       <c r="B844" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D844">
         <v>1009.50035186488</v>
@@ -14539,7 +14535,7 @@
         <v>230</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1" s="1">
         <v>459</v>
@@ -14553,7 +14549,7 @@
         <v>230</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D2" s="1">
         <v>472</v>
@@ -14567,7 +14563,7 @@
         <v>230</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D3" s="1">
         <v>474</v>
@@ -14581,7 +14577,7 @@
         <v>230</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D4" s="1">
         <v>500</v>
@@ -14595,7 +14591,7 @@
         <v>230</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D5" s="1">
         <v>516</v>
@@ -14609,7 +14605,7 @@
         <v>230</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D6" s="1">
         <v>544</v>
@@ -14623,7 +14619,7 @@
         <v>230</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D7" s="1">
         <v>570</v>
@@ -14637,7 +14633,7 @@
         <v>230</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D8" s="1">
         <v>600</v>
@@ -14651,7 +14647,7 @@
         <v>230</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D9" s="1">
         <v>622</v>
@@ -14665,7 +14661,7 @@
         <v>230</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D10" s="1">
         <v>648</v>
@@ -14679,7 +14675,7 @@
         <v>230</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" s="1">
         <v>671</v>
@@ -14693,7 +14689,7 @@
         <v>230</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D12" s="1">
         <v>671</v>
@@ -14707,7 +14703,7 @@
         <v>230</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D13" s="1">
         <v>697</v>
@@ -14721,7 +14717,7 @@
         <v>230</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D14" s="1">
         <v>720</v>
